--- a/backend/data/financials_by_company/1165.HK.xlsx
+++ b/backend/data/financials_by_company/1165.HK.xlsx
@@ -667,586 +667,586 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-712470</v>
+        <v>-79327875</v>
       </c>
       <c r="C2" t="n">
         <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-16344000</v>
+        <v>586274000</v>
       </c>
       <c r="E2" t="n">
-        <v>-4318000</v>
+        <v>-480775000</v>
       </c>
       <c r="F2" t="n">
-        <v>-4318000</v>
+        <v>-480775000</v>
       </c>
       <c r="G2" t="n">
-        <v>-435480000</v>
+        <v>-872068000</v>
       </c>
       <c r="H2" t="n">
-        <v>100556000</v>
+        <v>324780000</v>
       </c>
       <c r="I2" t="n">
-        <v>118712000</v>
+        <v>353429000</v>
       </c>
       <c r="J2" t="n">
-        <v>-20662000</v>
+        <v>105499000</v>
       </c>
       <c r="K2" t="n">
-        <v>-121218000</v>
+        <v>-219281000</v>
       </c>
       <c r="L2" t="n">
-        <v>-313408000</v>
+        <v>-574871000</v>
       </c>
       <c r="M2" t="n">
-        <v>318037000</v>
+        <v>592903000</v>
       </c>
       <c r="N2" t="n">
-        <v>4629000</v>
+        <v>18032000</v>
       </c>
       <c r="O2" t="n">
-        <v>-431874470</v>
+        <v>-470620875</v>
       </c>
       <c r="P2" t="n">
-        <v>-435480000</v>
+        <v>-745212000</v>
       </c>
       <c r="Q2" t="n">
-        <v>211011000</v>
+        <v>442454000</v>
       </c>
       <c r="R2" t="n">
-        <v>5082375490</v>
+        <v>4982375490</v>
       </c>
       <c r="S2" t="n">
-        <v>5082375490</v>
+        <v>4982375490</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0857</v>
+        <v>-0.1496</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0857</v>
+        <v>-0.1496</v>
       </c>
       <c r="V2" t="n">
-        <v>-435480000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>-745212000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
-        <v>-435480000</v>
+        <v>-745212000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-435480000</v>
+        <v>-745212000</v>
       </c>
       <c r="AA2" t="n">
-        <v>4789000</v>
+        <v>-54052000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-440269000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>-691160000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>126856000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-440269000</v>
+        <v>-818016000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1014000</v>
+        <v>5832000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-439255000</v>
+        <v>-812184000</v>
       </c>
       <c r="AG2" t="n">
-        <v>7208000</v>
+        <v>-23229000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4318000</v>
+        <v>-480775000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-9636000</v>
+        <v>243122000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>112000</v>
+        <v>82332000</v>
       </c>
       <c r="AK2" t="n">
-        <v>13842000</v>
+        <v>155321000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-313408000</v>
+        <v>-574871000</v>
       </c>
       <c r="AM2" t="n">
-        <v>318037000</v>
+        <v>592903000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4629000</v>
+        <v>18032000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-51218000</v>
+        <v>207732000</v>
       </c>
       <c r="AP2" t="n">
-        <v>92299000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>32084000</v>
-      </c>
+        <v>89025000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>60215000</v>
+        <v>107935000</v>
       </c>
       <c r="AS2" t="n">
-        <v>60215000</v>
+        <v>107935000</v>
       </c>
       <c r="AT2" t="n">
-        <v>41081000</v>
+        <v>296757000</v>
       </c>
       <c r="AU2" t="n">
-        <v>118712000</v>
+        <v>353429000</v>
       </c>
       <c r="AV2" t="n">
-        <v>159793000</v>
+        <v>650186000</v>
       </c>
       <c r="AW2" t="n">
-        <v>159793000</v>
+        <v>650186000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-13825680</v>
+        <v>18498480</v>
       </c>
       <c r="C3" t="n">
         <v>0.165</v>
       </c>
       <c r="D3" t="n">
-        <v>127696000</v>
+        <v>299429000</v>
       </c>
       <c r="E3" t="n">
-        <v>-83792000</v>
+        <v>112112000</v>
       </c>
       <c r="F3" t="n">
-        <v>-83792000</v>
+        <v>112112000</v>
       </c>
       <c r="G3" t="n">
-        <v>-449458000</v>
+        <v>-173900000</v>
       </c>
       <c r="H3" t="n">
-        <v>112155000</v>
+        <v>154528000</v>
       </c>
       <c r="I3" t="n">
-        <v>120296000</v>
+        <v>168725000</v>
       </c>
       <c r="J3" t="n">
-        <v>43904000</v>
+        <v>411541000</v>
       </c>
       <c r="K3" t="n">
-        <v>-68251000</v>
+        <v>257013000</v>
       </c>
       <c r="L3" t="n">
-        <v>-389406000</v>
+        <v>-417103000</v>
       </c>
       <c r="M3" t="n">
-        <v>398163000</v>
+        <v>430829000</v>
       </c>
       <c r="N3" t="n">
-        <v>8757000</v>
+        <v>13726000</v>
       </c>
       <c r="O3" t="n">
-        <v>-379491680</v>
+        <v>-267513520</v>
       </c>
       <c r="P3" t="n">
-        <v>-449458000</v>
+        <v>-173900000</v>
       </c>
       <c r="Q3" t="n">
-        <v>151514000</v>
+        <v>123755000</v>
       </c>
       <c r="R3" t="n">
-        <v>5082375490</v>
+        <v>4991690558</v>
       </c>
       <c r="S3" t="n">
-        <v>5082375490</v>
+        <v>4991690558</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.0348</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.0348</v>
       </c>
       <c r="V3" t="n">
-        <v>-449458000</v>
+        <v>-173900000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-449458000</v>
+        <v>-173900000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-449458000</v>
+        <v>-173900000</v>
       </c>
       <c r="AA3" t="n">
-        <v>21582000</v>
+        <v>4727000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-471040000</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>-178627000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
       <c r="AD3" t="n">
-        <v>-471040000</v>
+        <v>-178627000</v>
       </c>
       <c r="AE3" t="n">
-        <v>4626000</v>
+        <v>4811000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-466414000</v>
+        <v>-173816000</v>
       </c>
       <c r="AG3" t="n">
-        <v>16118000</v>
+        <v>170194000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-83792000</v>
+        <v>112112000</v>
       </c>
       <c r="AI3" t="n">
-        <v>21039000</v>
+        <v>12763000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25000</v>
+        <v>12191000</v>
       </c>
       <c r="AK3" t="n">
-        <v>62728000</v>
+        <v>-137066000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-389406000</v>
+        <v>-417103000</v>
       </c>
       <c r="AM3" t="n">
-        <v>398163000</v>
+        <v>430829000</v>
       </c>
       <c r="AN3" t="n">
-        <v>8757000</v>
+        <v>13726000</v>
       </c>
       <c r="AO3" t="n">
-        <v>86967000</v>
+        <v>189388000</v>
       </c>
       <c r="AP3" t="n">
-        <v>31218000</v>
+        <v>-44970000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-47340000</v>
+        <v>-41207000</v>
       </c>
       <c r="AR3" t="n">
-        <v>78558000</v>
+        <v>88314000</v>
       </c>
       <c r="AS3" t="n">
-        <v>78558000</v>
+        <v>88314000</v>
       </c>
       <c r="AT3" t="n">
-        <v>118185000</v>
+        <v>144418000</v>
       </c>
       <c r="AU3" t="n">
-        <v>120296000</v>
+        <v>168725000</v>
       </c>
       <c r="AV3" t="n">
-        <v>238481000</v>
+        <v>313143000</v>
       </c>
       <c r="AW3" t="n">
-        <v>238481000</v>
+        <v>313143000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>18498480</v>
+        <v>-13825680</v>
       </c>
       <c r="C4" t="n">
         <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>299429000</v>
+        <v>127696000</v>
       </c>
       <c r="E4" t="n">
-        <v>112112000</v>
+        <v>-83792000</v>
       </c>
       <c r="F4" t="n">
-        <v>112112000</v>
+        <v>-83792000</v>
       </c>
       <c r="G4" t="n">
-        <v>-173900000</v>
+        <v>-449458000</v>
       </c>
       <c r="H4" t="n">
-        <v>154528000</v>
+        <v>112155000</v>
       </c>
       <c r="I4" t="n">
-        <v>168725000</v>
+        <v>120296000</v>
       </c>
       <c r="J4" t="n">
-        <v>411541000</v>
+        <v>43904000</v>
       </c>
       <c r="K4" t="n">
-        <v>257013000</v>
+        <v>-68251000</v>
       </c>
       <c r="L4" t="n">
-        <v>-417103000</v>
+        <v>-389406000</v>
       </c>
       <c r="M4" t="n">
-        <v>430829000</v>
+        <v>398163000</v>
       </c>
       <c r="N4" t="n">
-        <v>13726000</v>
+        <v>8757000</v>
       </c>
       <c r="O4" t="n">
-        <v>-267513520</v>
+        <v>-379491680</v>
       </c>
       <c r="P4" t="n">
-        <v>-173900000</v>
+        <v>-449458000</v>
       </c>
       <c r="Q4" t="n">
-        <v>123755000</v>
+        <v>151514000</v>
       </c>
       <c r="R4" t="n">
-        <v>4991690558</v>
+        <v>5082375490</v>
       </c>
       <c r="S4" t="n">
-        <v>4991690558</v>
+        <v>5082375490</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0348</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0348</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-173900000</v>
+        <v>-449458000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-173900000</v>
+        <v>-449458000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-173900000</v>
+        <v>-449458000</v>
       </c>
       <c r="AA4" t="n">
-        <v>4727000</v>
+        <v>21582000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-178627000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
+        <v>-471040000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-178627000</v>
+        <v>-471040000</v>
       </c>
       <c r="AE4" t="n">
-        <v>4811000</v>
+        <v>4626000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-173816000</v>
+        <v>-466414000</v>
       </c>
       <c r="AG4" t="n">
-        <v>170194000</v>
+        <v>16118000</v>
       </c>
       <c r="AH4" t="n">
-        <v>112112000</v>
+        <v>-83792000</v>
       </c>
       <c r="AI4" t="n">
-        <v>12763000</v>
+        <v>21039000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12191000</v>
+        <v>25000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-137066000</v>
+        <v>62728000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-417103000</v>
+        <v>-389406000</v>
       </c>
       <c r="AM4" t="n">
-        <v>430829000</v>
+        <v>398163000</v>
       </c>
       <c r="AN4" t="n">
-        <v>13726000</v>
+        <v>8757000</v>
       </c>
       <c r="AO4" t="n">
-        <v>189388000</v>
+        <v>86967000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-44970000</v>
+        <v>31218000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-41207000</v>
+        <v>-47340000</v>
       </c>
       <c r="AR4" t="n">
-        <v>88314000</v>
+        <v>78558000</v>
       </c>
       <c r="AS4" t="n">
-        <v>88314000</v>
+        <v>78558000</v>
       </c>
       <c r="AT4" t="n">
-        <v>144418000</v>
+        <v>118185000</v>
       </c>
       <c r="AU4" t="n">
-        <v>168725000</v>
+        <v>120296000</v>
       </c>
       <c r="AV4" t="n">
-        <v>313143000</v>
+        <v>238481000</v>
       </c>
       <c r="AW4" t="n">
-        <v>313143000</v>
+        <v>238481000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-79327875</v>
+        <v>-712470</v>
       </c>
       <c r="C5" t="n">
         <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>586274000</v>
+        <v>-16344000</v>
       </c>
       <c r="E5" t="n">
-        <v>-480775000</v>
+        <v>-4318000</v>
       </c>
       <c r="F5" t="n">
-        <v>-480775000</v>
+        <v>-4318000</v>
       </c>
       <c r="G5" t="n">
-        <v>-872068000</v>
+        <v>-435480000</v>
       </c>
       <c r="H5" t="n">
-        <v>324780000</v>
+        <v>100556000</v>
       </c>
       <c r="I5" t="n">
-        <v>353429000</v>
+        <v>118712000</v>
       </c>
       <c r="J5" t="n">
-        <v>105499000</v>
+        <v>-20662000</v>
       </c>
       <c r="K5" t="n">
-        <v>-219281000</v>
+        <v>-121218000</v>
       </c>
       <c r="L5" t="n">
-        <v>-574871000</v>
+        <v>-313408000</v>
       </c>
       <c r="M5" t="n">
-        <v>592903000</v>
+        <v>318037000</v>
       </c>
       <c r="N5" t="n">
-        <v>18032000</v>
+        <v>4629000</v>
       </c>
       <c r="O5" t="n">
-        <v>-470620875</v>
+        <v>-431874470</v>
       </c>
       <c r="P5" t="n">
-        <v>-745212000</v>
+        <v>-435480000</v>
       </c>
       <c r="Q5" t="n">
-        <v>442454000</v>
+        <v>211011000</v>
       </c>
       <c r="R5" t="n">
-        <v>4982375490</v>
+        <v>5082375490</v>
       </c>
       <c r="S5" t="n">
-        <v>4982375490</v>
+        <v>5082375490</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1496</v>
+        <v>-0.0857</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1496</v>
+        <v>-0.0857</v>
       </c>
       <c r="V5" t="n">
-        <v>-745212000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
+        <v>-435480000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-745212000</v>
+        <v>-435480000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-745212000</v>
+        <v>-435480000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-54052000</v>
+        <v>4789000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-691160000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>126856000</v>
-      </c>
+        <v>-440269000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>-818016000</v>
+        <v>-440269000</v>
       </c>
       <c r="AE5" t="n">
-        <v>5832000</v>
+        <v>1014000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-812184000</v>
+        <v>-439255000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-23229000</v>
+        <v>7208000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-480775000</v>
+        <v>-4318000</v>
       </c>
       <c r="AI5" t="n">
-        <v>243122000</v>
+        <v>-9636000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>82332000</v>
+        <v>112000</v>
       </c>
       <c r="AK5" t="n">
-        <v>155321000</v>
+        <v>13842000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-574871000</v>
+        <v>-313408000</v>
       </c>
       <c r="AM5" t="n">
-        <v>592903000</v>
+        <v>318037000</v>
       </c>
       <c r="AN5" t="n">
-        <v>18032000</v>
+        <v>4629000</v>
       </c>
       <c r="AO5" t="n">
-        <v>207732000</v>
+        <v>-51218000</v>
       </c>
       <c r="AP5" t="n">
-        <v>89025000</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>92299000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>32084000</v>
+      </c>
       <c r="AR5" t="n">
-        <v>107935000</v>
+        <v>60215000</v>
       </c>
       <c r="AS5" t="n">
-        <v>107935000</v>
+        <v>60215000</v>
       </c>
       <c r="AT5" t="n">
-        <v>296757000</v>
+        <v>41081000</v>
       </c>
       <c r="AU5" t="n">
-        <v>353429000</v>
+        <v>118712000</v>
       </c>
       <c r="AV5" t="n">
-        <v>650186000</v>
+        <v>159793000</v>
       </c>
       <c r="AW5" t="n">
-        <v>650186000</v>
+        <v>159793000</v>
       </c>
     </row>
   </sheetData>
@@ -1622,116 +1622,122 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>5082375490</v>
+        <v>4982375490</v>
       </c>
       <c r="C2" t="n">
-        <v>5082375490</v>
+        <v>4982375490</v>
       </c>
       <c r="D2" t="n">
-        <v>3646170000</v>
+        <v>5849760000</v>
       </c>
       <c r="E2" t="n">
-        <v>3683434000</v>
+        <v>5933180000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1990457000</v>
+        <v>-1046415000</v>
       </c>
       <c r="G2" t="n">
-        <v>1687171000</v>
+        <v>4985599000</v>
       </c>
       <c r="H2" t="n">
-        <v>-2587807000</v>
+        <v>-1270195000</v>
       </c>
       <c r="I2" t="n">
-        <v>-1990457000</v>
+        <v>-1046415000</v>
       </c>
       <c r="J2" t="n">
-        <v>24187000</v>
+        <v>27715000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1972076000</v>
+        <v>-919866000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1527919000</v>
+        <v>968100000</v>
       </c>
       <c r="M2" t="n">
-        <v>-1908577000</v>
+        <v>-825269000</v>
       </c>
       <c r="N2" t="n">
-        <v>63499000</v>
+        <v>94597000</v>
       </c>
       <c r="O2" t="n">
-        <v>-1972076000</v>
+        <v>-919866000</v>
       </c>
       <c r="P2" t="n">
-        <v>677127000</v>
+        <v>879850000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-7698843000</v>
+        <v>-6842728000</v>
       </c>
       <c r="R2" t="n">
-        <v>6078548000</v>
+        <v>6076424000</v>
       </c>
       <c r="S2" t="n">
-        <v>41641000</v>
+        <v>40756000</v>
       </c>
       <c r="T2" t="n">
-        <v>41641000</v>
+        <v>40756000</v>
       </c>
       <c r="U2" t="n">
-        <v>4961981000</v>
+        <v>7632260000</v>
       </c>
       <c r="V2" t="n">
-        <v>455104000</v>
+        <v>1901194000</v>
       </c>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" t="n">
-        <v>455104000</v>
+        <v>1901194000</v>
       </c>
       <c r="Z2" t="n">
-        <v>10947000</v>
+        <v>13228000</v>
       </c>
       <c r="AA2" t="n">
-        <v>444157000</v>
+        <v>1887966000</v>
       </c>
       <c r="AB2" t="n">
-        <v>4506877000</v>
+        <v>5731066000</v>
       </c>
       <c r="AC2" t="n">
-        <v>3228330000</v>
+        <v>4031986000</v>
       </c>
       <c r="AD2" t="n">
-        <v>13240000</v>
+        <v>14487000</v>
       </c>
       <c r="AE2" t="n">
-        <v>3215090000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>4017499000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>201017000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>1266401000</v>
+        <v>725544000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1258124000</v>
+        <v>706181000</v>
       </c>
       <c r="AI2" t="n">
-        <v>5587000</v>
+        <v>11378000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2690000</v>
+        <v>7985000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3053404000</v>
+        <v>6806991000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1134334000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>2346120000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>23033000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>17779000</v>
+        <v>46094000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000000</v>
@@ -1740,85 +1746,99 @@
         <v>1000000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>39098000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>36109000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
       <c r="AS2" t="n">
-        <v>39098000</v>
+        <v>36109000</v>
       </c>
       <c r="AT2" t="n">
-        <v>18381000</v>
+        <v>126549000</v>
       </c>
       <c r="AU2" t="n">
-        <v>18381000</v>
+        <v>126549000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1039525000</v>
+        <v>2013876000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-794328000</v>
+        <v>-970125000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1833853000</v>
+        <v>2984001000</v>
       </c>
       <c r="AY2" t="n">
-        <v>57544000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>62398000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>69669000</v>
+      </c>
       <c r="BA2" t="n">
-        <v>28465000</v>
+        <v>28193000</v>
       </c>
       <c r="BB2" t="n">
-        <v>2861000</v>
+        <v>2991000</v>
       </c>
       <c r="BC2" t="n">
-        <v>35814000</v>
+        <v>53035000</v>
       </c>
       <c r="BD2" t="n">
-        <v>1709169000</v>
+        <v>2837384000</v>
       </c>
       <c r="BE2" t="n">
-        <v>1919070000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>4460871000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1273686000</v>
+      </c>
       <c r="BG2" t="n">
-        <v>5749000</v>
+        <v>11177000</v>
       </c>
       <c r="BH2" t="n">
-        <v>106760000</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
+        <v>107802000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
       <c r="BM2" t="n">
-        <v>1760627000</v>
+        <v>2929743000</v>
       </c>
       <c r="BN2" t="n">
-        <v>6618000</v>
+        <v>34419000</v>
       </c>
       <c r="BO2" t="n">
-        <v>26239000</v>
+        <v>48339000</v>
       </c>
       <c r="BP2" t="n">
-        <v>-11135000</v>
+        <v>-3437000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>37374000</v>
+        <v>51776000</v>
       </c>
       <c r="BR2" t="n">
-        <v>13077000</v>
+        <v>55705000</v>
       </c>
       <c r="BS2" t="n">
-        <v>13077000</v>
+        <v>55705000</v>
       </c>
       <c r="BT2" t="n">
-        <v>13077000</v>
+        <v>55705000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>5082375490</v>
@@ -1827,46 +1847,46 @@
         <v>5082375490</v>
       </c>
       <c r="D3" t="n">
-        <v>3516085000</v>
+        <v>4458996000</v>
       </c>
       <c r="E3" t="n">
-        <v>3641246000</v>
+        <v>5027160000</v>
       </c>
       <c r="F3" t="n">
-        <v>-1572444000</v>
+        <v>-1202059000</v>
       </c>
       <c r="G3" t="n">
-        <v>2076941000</v>
+        <v>3900870000</v>
       </c>
       <c r="H3" t="n">
-        <v>-1770582000</v>
+        <v>-2024843000</v>
       </c>
       <c r="I3" t="n">
-        <v>-1572444000</v>
+        <v>-1202059000</v>
       </c>
       <c r="J3" t="n">
-        <v>27715000</v>
+        <v>35546000</v>
       </c>
       <c r="K3" t="n">
-        <v>-1536590000</v>
+        <v>-1090744000</v>
       </c>
       <c r="L3" t="n">
-        <v>-622924000</v>
+        <v>-458874000</v>
       </c>
       <c r="M3" t="n">
-        <v>-1466122000</v>
+        <v>-998694000</v>
       </c>
       <c r="N3" t="n">
-        <v>70468000</v>
+        <v>92050000</v>
       </c>
       <c r="O3" t="n">
-        <v>-1536590000</v>
+        <v>-1090744000</v>
       </c>
       <c r="P3" t="n">
-        <v>761381000</v>
+        <v>879850000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-7347617000</v>
+        <v>-7016628000</v>
       </c>
       <c r="R3" t="n">
         <v>6078548000</v>
@@ -1878,58 +1898,60 @@
         <v>41641000</v>
       </c>
       <c r="U3" t="n">
-        <v>4715761000</v>
+        <v>6057492000</v>
       </c>
       <c r="V3" t="n">
-        <v>928510000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>419815000</v>
-      </c>
+        <v>652494000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>928510000</v>
+        <v>652494000</v>
       </c>
       <c r="Z3" t="n">
-        <v>14844000</v>
+        <v>20624000</v>
       </c>
       <c r="AA3" t="n">
-        <v>913666000</v>
+        <v>631870000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3787251000</v>
+        <v>5404998000</v>
       </c>
       <c r="AC3" t="n">
-        <v>2712736000</v>
+        <v>4374666000</v>
       </c>
       <c r="AD3" t="n">
-        <v>12871000</v>
+        <v>14922000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2699865000</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>4359744000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2632000</v>
+      </c>
       <c r="AG3" t="n">
-        <v>1062595000</v>
+        <v>991751000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1045535000</v>
+        <v>969827000</v>
       </c>
       <c r="AI3" t="n">
-        <v>15705000</v>
+        <v>15716000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1355000</v>
+        <v>6208000</v>
       </c>
       <c r="AK3" t="n">
-        <v>3249639000</v>
+        <v>5058798000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1232970000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>1678643000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>25814000</v>
+      </c>
       <c r="AN3" t="n">
-        <v>12921000</v>
+        <v>25814000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000000</v>
@@ -1938,89 +1960,91 @@
         <v>1000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>37451000</v>
+        <v>35649000</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>37451000</v>
+        <v>35649000</v>
       </c>
       <c r="AT3" t="n">
-        <v>35854000</v>
+        <v>111315000</v>
       </c>
       <c r="AU3" t="n">
-        <v>35854000</v>
+        <v>111315000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1128261000</v>
+        <v>1492290000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-711300000</v>
+        <v>-760964000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1839561000</v>
+        <v>2253254000</v>
       </c>
       <c r="AY3" t="n">
-        <v>58743000</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>59511000</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>88698000</v>
+      </c>
       <c r="BA3" t="n">
-        <v>27870000</v>
+        <v>26037000</v>
       </c>
       <c r="BB3" t="n">
-        <v>6178000</v>
+        <v>12522000</v>
       </c>
       <c r="BC3" t="n">
-        <v>37896000</v>
+        <v>50509000</v>
       </c>
       <c r="BD3" t="n">
-        <v>1708874000</v>
+        <v>2104675000</v>
       </c>
       <c r="BE3" t="n">
-        <v>2016669000</v>
+        <v>3380155000</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>649583000</v>
       </c>
       <c r="BG3" t="n">
-        <v>6417000</v>
+        <v>21932000</v>
       </c>
       <c r="BH3" t="n">
-        <v>125874000</v>
+        <v>113279000</v>
       </c>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="n">
-        <v>1745491000</v>
+        <v>1983822000</v>
       </c>
       <c r="BN3" t="n">
-        <v>7569000</v>
+        <v>12109000</v>
       </c>
       <c r="BO3" t="n">
-        <v>33872000</v>
+        <v>66812000</v>
       </c>
       <c r="BP3" t="n">
-        <v>-5824000</v>
+        <v>-5128000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>39696000</v>
+        <v>71940000</v>
       </c>
       <c r="BR3" t="n">
-        <v>97446000</v>
+        <v>532618000</v>
       </c>
       <c r="BS3" t="n">
-        <v>97446000</v>
+        <v>532618000</v>
       </c>
       <c r="BT3" t="n">
-        <v>97446000</v>
+        <v>532618000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>5082375490</v>
@@ -2029,46 +2053,46 @@
         <v>5082375490</v>
       </c>
       <c r="D4" t="n">
-        <v>4458996000</v>
+        <v>3516085000</v>
       </c>
       <c r="E4" t="n">
-        <v>5027160000</v>
+        <v>3641246000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1202059000</v>
+        <v>-1572444000</v>
       </c>
       <c r="G4" t="n">
-        <v>3900870000</v>
+        <v>2076941000</v>
       </c>
       <c r="H4" t="n">
-        <v>-2024843000</v>
+        <v>-1770582000</v>
       </c>
       <c r="I4" t="n">
-        <v>-1202059000</v>
+        <v>-1572444000</v>
       </c>
       <c r="J4" t="n">
-        <v>35546000</v>
+        <v>27715000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1090744000</v>
+        <v>-1536590000</v>
       </c>
       <c r="L4" t="n">
-        <v>-458874000</v>
+        <v>-622924000</v>
       </c>
       <c r="M4" t="n">
-        <v>-998694000</v>
+        <v>-1466122000</v>
       </c>
       <c r="N4" t="n">
-        <v>92050000</v>
+        <v>70468000</v>
       </c>
       <c r="O4" t="n">
-        <v>-1090744000</v>
+        <v>-1536590000</v>
       </c>
       <c r="P4" t="n">
-        <v>879850000</v>
+        <v>761381000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-7016628000</v>
+        <v>-7347617000</v>
       </c>
       <c r="R4" t="n">
         <v>6078548000</v>
@@ -2080,60 +2104,58 @@
         <v>41641000</v>
       </c>
       <c r="U4" t="n">
-        <v>6057492000</v>
+        <v>4715761000</v>
       </c>
       <c r="V4" t="n">
-        <v>652494000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>928510000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>419815000</v>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>652494000</v>
+        <v>928510000</v>
       </c>
       <c r="Z4" t="n">
-        <v>20624000</v>
+        <v>14844000</v>
       </c>
       <c r="AA4" t="n">
-        <v>631870000</v>
+        <v>913666000</v>
       </c>
       <c r="AB4" t="n">
-        <v>5404998000</v>
+        <v>3787251000</v>
       </c>
       <c r="AC4" t="n">
-        <v>4374666000</v>
+        <v>2712736000</v>
       </c>
       <c r="AD4" t="n">
-        <v>14922000</v>
+        <v>12871000</v>
       </c>
       <c r="AE4" t="n">
-        <v>4359744000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2632000</v>
-      </c>
+        <v>2699865000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>991751000</v>
+        <v>1062595000</v>
       </c>
       <c r="AH4" t="n">
-        <v>969827000</v>
+        <v>1045535000</v>
       </c>
       <c r="AI4" t="n">
-        <v>15716000</v>
+        <v>15705000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6208000</v>
+        <v>1355000</v>
       </c>
       <c r="AK4" t="n">
-        <v>5058798000</v>
+        <v>3249639000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1678643000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>25814000</v>
-      </c>
+        <v>1232970000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>25814000</v>
+        <v>12921000</v>
       </c>
       <c r="AO4" t="n">
         <v>1000000</v>
@@ -2142,206 +2164,198 @@
         <v>1000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>35649000</v>
+        <v>37451000</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>35649000</v>
+        <v>37451000</v>
       </c>
       <c r="AT4" t="n">
-        <v>111315000</v>
+        <v>35854000</v>
       </c>
       <c r="AU4" t="n">
-        <v>111315000</v>
+        <v>35854000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1492290000</v>
+        <v>1128261000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-760964000</v>
+        <v>-711300000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2253254000</v>
+        <v>1839561000</v>
       </c>
       <c r="AY4" t="n">
-        <v>59511000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>88698000</v>
-      </c>
+        <v>58743000</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>26037000</v>
+        <v>27870000</v>
       </c>
       <c r="BB4" t="n">
-        <v>12522000</v>
+        <v>6178000</v>
       </c>
       <c r="BC4" t="n">
-        <v>50509000</v>
+        <v>37896000</v>
       </c>
       <c r="BD4" t="n">
-        <v>2104675000</v>
+        <v>1708874000</v>
       </c>
       <c r="BE4" t="n">
-        <v>3380155000</v>
+        <v>2016669000</v>
       </c>
       <c r="BF4" t="n">
-        <v>649583000</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>21932000</v>
+        <v>6417000</v>
       </c>
       <c r="BH4" t="n">
-        <v>113279000</v>
+        <v>125874000</v>
       </c>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>1983822000</v>
+        <v>1745491000</v>
       </c>
       <c r="BN4" t="n">
-        <v>12109000</v>
+        <v>7569000</v>
       </c>
       <c r="BO4" t="n">
-        <v>66812000</v>
+        <v>33872000</v>
       </c>
       <c r="BP4" t="n">
-        <v>-5128000</v>
+        <v>-5824000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>71940000</v>
+        <v>39696000</v>
       </c>
       <c r="BR4" t="n">
-        <v>532618000</v>
+        <v>97446000</v>
       </c>
       <c r="BS4" t="n">
-        <v>532618000</v>
+        <v>97446000</v>
       </c>
       <c r="BT4" t="n">
-        <v>532618000</v>
+        <v>97446000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>4982375490</v>
+        <v>5082375490</v>
       </c>
       <c r="C5" t="n">
-        <v>4982375490</v>
+        <v>5082375490</v>
       </c>
       <c r="D5" t="n">
-        <v>5849760000</v>
+        <v>3646170000</v>
       </c>
       <c r="E5" t="n">
-        <v>5933180000</v>
+        <v>3683434000</v>
       </c>
       <c r="F5" t="n">
-        <v>-1046415000</v>
+        <v>-1990457000</v>
       </c>
       <c r="G5" t="n">
-        <v>4985599000</v>
+        <v>1687171000</v>
       </c>
       <c r="H5" t="n">
-        <v>-1270195000</v>
+        <v>-2587807000</v>
       </c>
       <c r="I5" t="n">
-        <v>-1046415000</v>
+        <v>-1990457000</v>
       </c>
       <c r="J5" t="n">
-        <v>27715000</v>
+        <v>24187000</v>
       </c>
       <c r="K5" t="n">
-        <v>-919866000</v>
+        <v>-1972076000</v>
       </c>
       <c r="L5" t="n">
-        <v>968100000</v>
+        <v>-1527919000</v>
       </c>
       <c r="M5" t="n">
-        <v>-825269000</v>
+        <v>-1908577000</v>
       </c>
       <c r="N5" t="n">
-        <v>94597000</v>
+        <v>63499000</v>
       </c>
       <c r="O5" t="n">
-        <v>-919866000</v>
+        <v>-1972076000</v>
       </c>
       <c r="P5" t="n">
-        <v>879850000</v>
+        <v>677127000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6842728000</v>
+        <v>-7698843000</v>
       </c>
       <c r="R5" t="n">
-        <v>6076424000</v>
+        <v>6078548000</v>
       </c>
       <c r="S5" t="n">
-        <v>40756000</v>
+        <v>41641000</v>
       </c>
       <c r="T5" t="n">
-        <v>40756000</v>
+        <v>41641000</v>
       </c>
       <c r="U5" t="n">
-        <v>7632260000</v>
+        <v>4961981000</v>
       </c>
       <c r="V5" t="n">
-        <v>1901194000</v>
+        <v>455104000</v>
       </c>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>1901194000</v>
+        <v>455104000</v>
       </c>
       <c r="Z5" t="n">
-        <v>13228000</v>
+        <v>10947000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1887966000</v>
+        <v>444157000</v>
       </c>
       <c r="AB5" t="n">
-        <v>5731066000</v>
+        <v>4506877000</v>
       </c>
       <c r="AC5" t="n">
-        <v>4031986000</v>
+        <v>3228330000</v>
       </c>
       <c r="AD5" t="n">
-        <v>14487000</v>
+        <v>13240000</v>
       </c>
       <c r="AE5" t="n">
-        <v>4017499000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>201017000</v>
-      </c>
+        <v>3215090000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>725544000</v>
+        <v>1266401000</v>
       </c>
       <c r="AH5" t="n">
-        <v>706181000</v>
+        <v>1258124000</v>
       </c>
       <c r="AI5" t="n">
-        <v>11378000</v>
+        <v>5587000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>7985000</v>
+        <v>2690000</v>
       </c>
       <c r="AK5" t="n">
-        <v>6806991000</v>
+        <v>3053404000</v>
       </c>
       <c r="AL5" t="n">
-        <v>2346120000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>23033000</v>
-      </c>
+        <v>1134334000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>46094000</v>
+        <v>17779000</v>
       </c>
       <c r="AO5" t="n">
         <v>1000000</v>
@@ -2350,94 +2364,80 @@
         <v>1000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>36109000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
+        <v>39098000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>36109000</v>
+        <v>39098000</v>
       </c>
       <c r="AT5" t="n">
-        <v>126549000</v>
+        <v>18381000</v>
       </c>
       <c r="AU5" t="n">
-        <v>126549000</v>
+        <v>18381000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2013876000</v>
+        <v>1039525000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-970125000</v>
+        <v>-794328000</v>
       </c>
       <c r="AX5" t="n">
-        <v>2984001000</v>
+        <v>1833853000</v>
       </c>
       <c r="AY5" t="n">
-        <v>62398000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>69669000</v>
-      </c>
+        <v>57544000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>28193000</v>
+        <v>28465000</v>
       </c>
       <c r="BB5" t="n">
-        <v>2991000</v>
+        <v>2861000</v>
       </c>
       <c r="BC5" t="n">
-        <v>53035000</v>
+        <v>35814000</v>
       </c>
       <c r="BD5" t="n">
-        <v>2837384000</v>
+        <v>1709169000</v>
       </c>
       <c r="BE5" t="n">
-        <v>4460871000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1273686000</v>
-      </c>
+        <v>1919070000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>11177000</v>
+        <v>5749000</v>
       </c>
       <c r="BH5" t="n">
-        <v>107802000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
+        <v>106760000</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="n">
-        <v>2929743000</v>
+        <v>1760627000</v>
       </c>
       <c r="BN5" t="n">
-        <v>34419000</v>
+        <v>6618000</v>
       </c>
       <c r="BO5" t="n">
-        <v>48339000</v>
+        <v>26239000</v>
       </c>
       <c r="BP5" t="n">
-        <v>-3437000</v>
+        <v>-11135000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>51776000</v>
+        <v>37374000</v>
       </c>
       <c r="BR5" t="n">
-        <v>55705000</v>
+        <v>13077000</v>
       </c>
       <c r="BS5" t="n">
-        <v>55705000</v>
+        <v>13077000</v>
       </c>
       <c r="BT5" t="n">
-        <v>55705000</v>
+        <v>13077000</v>
       </c>
     </row>
   </sheetData>
@@ -2693,552 +2693,552 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-14279000</v>
+        <v>221397000</v>
       </c>
       <c r="C2" t="n">
-        <v>-17961000</v>
+        <v>-445059000</v>
       </c>
       <c r="D2" t="n">
-        <v>13500000</v>
+        <v>10000000</v>
       </c>
       <c r="E2" t="n">
-        <v>-9788000</v>
+        <v>-65389000</v>
       </c>
       <c r="F2" t="n">
-        <v>13077000</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>55705000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-25000</v>
+      </c>
       <c r="H2" t="n">
-        <v>97446000</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>226746000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-8000</v>
+      </c>
       <c r="J2" t="n">
-        <v>-84369000</v>
+        <v>-171008000</v>
       </c>
       <c r="K2" t="n">
-        <v>-101655000</v>
+        <v>-647955000</v>
       </c>
       <c r="L2" t="n">
-        <v>-10481000</v>
+        <v>-31475000</v>
       </c>
       <c r="M2" t="n">
-        <v>-81374000</v>
+        <v>-174814000</v>
       </c>
       <c r="N2" t="n">
-        <v>-4461000</v>
+        <v>-435059000</v>
       </c>
       <c r="O2" t="n">
-        <v>-4461000</v>
+        <v>-435059000</v>
       </c>
       <c r="P2" t="n">
-        <v>-17961000</v>
+        <v>-445059000</v>
       </c>
       <c r="Q2" t="n">
-        <v>13500000</v>
+        <v>10000000</v>
       </c>
       <c r="R2" t="n">
-        <v>21777000</v>
+        <v>190161000</v>
       </c>
       <c r="S2" t="n">
-        <v>668000</v>
+        <v>-61022000</v>
       </c>
       <c r="T2" t="n">
-        <v>440000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+        <v>2326000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-1000000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>30338000</v>
+        <v>299596000</v>
       </c>
       <c r="Z2" t="n">
-        <v>30338000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+        <v>299596000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-181000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-181000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-9669000</v>
+        <v>-53889000</v>
       </c>
       <c r="AD2" t="n">
-        <v>119000</v>
+        <v>11319000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-9788000</v>
+        <v>-65208000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-4491000</v>
+        <v>286786000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3225000</v>
+        <v>-14624000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-89896000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>-377229000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>5544000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>2472000</v>
+        <v>35273000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3122000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>12125000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-22538000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>-95490000</v>
+        <v>-407633000</v>
       </c>
       <c r="AN2" t="n">
-        <v>313408000</v>
+        <v>537787000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-16168000</v>
+        <v>54046000</v>
       </c>
       <c r="AP2" t="n">
-        <v>100556000</v>
+        <v>324780000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7316000</v>
+        <v>18241000</v>
       </c>
       <c r="AR2" t="n">
-        <v>93240000</v>
+        <v>306539000</v>
       </c>
       <c r="AS2" t="n">
-        <v>79166000</v>
+        <v>-62283000</v>
       </c>
       <c r="AT2" t="n">
-        <v>105000</v>
+        <v>-628000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1191000</v>
+        <v>302361000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-439255000</v>
+        <v>-678775000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>14400000</v>
+        <v>176275000</v>
       </c>
       <c r="C3" t="n">
-        <v>-127698000</v>
+        <v>-142243000</v>
       </c>
       <c r="D3" t="n">
-        <v>20000000</v>
+        <v>46001000</v>
       </c>
       <c r="E3" t="n">
-        <v>-29432000</v>
+        <v>-13808000</v>
       </c>
       <c r="F3" t="n">
-        <v>97446000</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>532618000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-19000</v>
+      </c>
       <c r="H3" t="n">
-        <v>532637000</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>55730000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
       <c r="J3" t="n">
-        <v>-435191000</v>
+        <v>476907000</v>
       </c>
       <c r="K3" t="n">
-        <v>-648264000</v>
+        <v>-1271202000</v>
       </c>
       <c r="L3" t="n">
-        <v>-466188000</v>
+        <v>-1035814000</v>
       </c>
       <c r="M3" t="n">
-        <v>-67721000</v>
+        <v>-131944000</v>
       </c>
       <c r="N3" t="n">
-        <v>-107698000</v>
+        <v>-96242000</v>
       </c>
       <c r="O3" t="n">
-        <v>-107698000</v>
+        <v>-96242000</v>
       </c>
       <c r="P3" t="n">
-        <v>-127698000</v>
+        <v>-142243000</v>
       </c>
       <c r="Q3" t="n">
-        <v>20000000</v>
+        <v>46001000</v>
       </c>
       <c r="R3" t="n">
-        <v>169241000</v>
+        <v>1558026000</v>
       </c>
       <c r="S3" t="n">
-        <v>21194000</v>
+        <v>54743000</v>
       </c>
       <c r="T3" t="n">
-        <v>4112000</v>
+        <v>4152000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1470000</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>46563000</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
+        <v>46563000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y3" t="n">
-        <v>173367000</v>
+        <v>1589953000</v>
       </c>
       <c r="Z3" t="n">
-        <v>173367000</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+        <v>1589953000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" t="n">
-        <v>-29432000</v>
+        <v>-13808000</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-29432000</v>
+        <v>-13808000</v>
       </c>
       <c r="AF3" t="n">
-        <v>43832000</v>
+        <v>190083000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-3711000</v>
+        <v>-3654000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-120357000</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>-67991000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>-29247000</v>
+        <v>5405000</v>
       </c>
       <c r="AK3" t="n">
-        <v>751000</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>-2553000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
       <c r="AM3" t="n">
-        <v>-90611000</v>
+        <v>-49720000</v>
       </c>
       <c r="AN3" t="n">
-        <v>388024000</v>
+        <v>226294000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-30037000</v>
+        <v>-37384000</v>
       </c>
       <c r="AP3" t="n">
-        <v>112155000</v>
+        <v>154528000</v>
       </c>
       <c r="AQ3" t="n">
         <v>15234000</v>
       </c>
       <c r="AR3" t="n">
-        <v>96921000</v>
+        <v>139294000</v>
       </c>
       <c r="AS3" t="n">
-        <v>98103000</v>
+        <v>203773000</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>28673000</v>
+        <v>21131000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-466414000</v>
+        <v>-173816000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>176275000</v>
+        <v>14400000</v>
       </c>
       <c r="C4" t="n">
-        <v>-142243000</v>
+        <v>-127698000</v>
       </c>
       <c r="D4" t="n">
-        <v>46001000</v>
+        <v>20000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-13808000</v>
+        <v>-29432000</v>
       </c>
       <c r="F4" t="n">
-        <v>532618000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-19000</v>
-      </c>
+        <v>97446000</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>55730000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+        <v>532637000</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>476907000</v>
+        <v>-435191000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1271202000</v>
+        <v>-648264000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1035814000</v>
+        <v>-466188000</v>
       </c>
       <c r="M4" t="n">
-        <v>-131944000</v>
+        <v>-67721000</v>
       </c>
       <c r="N4" t="n">
-        <v>-96242000</v>
+        <v>-107698000</v>
       </c>
       <c r="O4" t="n">
-        <v>-96242000</v>
+        <v>-107698000</v>
       </c>
       <c r="P4" t="n">
-        <v>-142243000</v>
+        <v>-127698000</v>
       </c>
       <c r="Q4" t="n">
-        <v>46001000</v>
+        <v>20000000</v>
       </c>
       <c r="R4" t="n">
-        <v>1558026000</v>
+        <v>169241000</v>
       </c>
       <c r="S4" t="n">
-        <v>54743000</v>
+        <v>21194000</v>
       </c>
       <c r="T4" t="n">
-        <v>4152000</v>
+        <v>4112000</v>
       </c>
       <c r="U4" t="n">
-        <v>1470000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>46563000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>46563000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>1589953000</v>
+        <v>173367000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1589953000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>173367000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>-13808000</v>
+        <v>-29432000</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-13808000</v>
+        <v>-29432000</v>
       </c>
       <c r="AF4" t="n">
-        <v>190083000</v>
+        <v>43832000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3654000</v>
+        <v>-3711000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-67991000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
+        <v>-120357000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>5405000</v>
+        <v>-29247000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-2553000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
+        <v>751000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>-49720000</v>
+        <v>-90611000</v>
       </c>
       <c r="AN4" t="n">
-        <v>226294000</v>
+        <v>388024000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-37384000</v>
+        <v>-30037000</v>
       </c>
       <c r="AP4" t="n">
-        <v>154528000</v>
+        <v>112155000</v>
       </c>
       <c r="AQ4" t="n">
         <v>15234000</v>
       </c>
       <c r="AR4" t="n">
-        <v>139294000</v>
+        <v>96921000</v>
       </c>
       <c r="AS4" t="n">
-        <v>203773000</v>
+        <v>98103000</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>21131000</v>
+        <v>28673000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-173816000</v>
+        <v>-466414000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>221397000</v>
+        <v>-14279000</v>
       </c>
       <c r="C5" t="n">
-        <v>-445059000</v>
+        <v>-17961000</v>
       </c>
       <c r="D5" t="n">
-        <v>10000000</v>
+        <v>13500000</v>
       </c>
       <c r="E5" t="n">
-        <v>-65389000</v>
+        <v>-9788000</v>
       </c>
       <c r="F5" t="n">
-        <v>55705000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-25000</v>
-      </c>
+        <v>13077000</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>226746000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-8000</v>
-      </c>
+        <v>97446000</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>-171008000</v>
+        <v>-84369000</v>
       </c>
       <c r="K5" t="n">
-        <v>-647955000</v>
+        <v>-101655000</v>
       </c>
       <c r="L5" t="n">
-        <v>-31475000</v>
+        <v>-10481000</v>
       </c>
       <c r="M5" t="n">
-        <v>-174814000</v>
+        <v>-81374000</v>
       </c>
       <c r="N5" t="n">
-        <v>-435059000</v>
+        <v>-4461000</v>
       </c>
       <c r="O5" t="n">
-        <v>-435059000</v>
+        <v>-4461000</v>
       </c>
       <c r="P5" t="n">
-        <v>-445059000</v>
+        <v>-17961000</v>
       </c>
       <c r="Q5" t="n">
-        <v>10000000</v>
+        <v>13500000</v>
       </c>
       <c r="R5" t="n">
-        <v>190161000</v>
+        <v>21777000</v>
       </c>
       <c r="S5" t="n">
-        <v>-61022000</v>
+        <v>668000</v>
       </c>
       <c r="T5" t="n">
-        <v>2326000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1000000</v>
-      </c>
+        <v>440000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>299596000</v>
+        <v>30338000</v>
       </c>
       <c r="Z5" t="n">
-        <v>299596000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-181000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-181000</v>
-      </c>
+        <v>30338000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-53889000</v>
+        <v>-9669000</v>
       </c>
       <c r="AD5" t="n">
-        <v>11319000</v>
+        <v>119000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-65208000</v>
+        <v>-9788000</v>
       </c>
       <c r="AF5" t="n">
-        <v>286786000</v>
+        <v>-4491000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-14624000</v>
+        <v>-3225000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-377229000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5544000</v>
-      </c>
+        <v>-89896000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>35273000</v>
+        <v>2472000</v>
       </c>
       <c r="AK5" t="n">
-        <v>12125000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-22538000</v>
-      </c>
+        <v>3122000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>-407633000</v>
+        <v>-95490000</v>
       </c>
       <c r="AN5" t="n">
-        <v>537787000</v>
+        <v>313408000</v>
       </c>
       <c r="AO5" t="n">
-        <v>54046000</v>
+        <v>-16168000</v>
       </c>
       <c r="AP5" t="n">
-        <v>324780000</v>
+        <v>100556000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18241000</v>
+        <v>7316000</v>
       </c>
       <c r="AR5" t="n">
-        <v>306539000</v>
+        <v>93240000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-62283000</v>
+        <v>79166000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-628000</v>
+        <v>105000</v>
       </c>
       <c r="AU5" t="n">
-        <v>302361000</v>
+        <v>-1191000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-678775000</v>
+        <v>-439255000</v>
       </c>
     </row>
   </sheetData>
@@ -3763,192 +3763,192 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Bo  Qiu', 'age': 44, 'title': 'Executive Director', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bin  Lu', 'age': 55, 'title': 'Company Secretary', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 2135007, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jibiao  Han', 'age': 42, 'title': 'Chairman &amp; CEO', 'yearBorn': 1983, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. David Robin  Hogg', 'age': 66, 'title': 'President of Europe', 'yearBorn': 1959, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Bo  Qiu', 'age': 44, 'title': 'Executive Director', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bin  Lu', 'age': 55, 'title': 'Company Secretary', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 2133306, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jibiao  Han', 'age': 42, 'title': 'Chairman &amp; CEO', 'yearBorn': 1983, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. David Robin  Hogg', 'age': 66, 'title': 'President of Europe', 'yearBorn': 1959, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4047,7 +4047,7 @@
         <v>9</v>
       </c>
       <c r="U2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="V2" t="n">
         <v>1735603200</v>
@@ -4091,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="AJ2" t="n">
         <v>4052000</v>
@@ -4145,7 +4145,7 @@
         <v>0.024</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.023915</v>
+        <v>0.02384</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
@@ -4183,7 +4183,7 @@
         <v>5082375490</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.49684283</v>
+        <v>-0.4965753</v>
       </c>
       <c r="BN2" t="n">
         <v>1735603200</v>
@@ -4210,7 +4210,7 @@
         <v>0.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -4313,141 +4313,141 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="CY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="n">
+          <t>SFCE</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>Shunfeng International Clean Energy Limited</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>1763522342</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>finmb_62168284</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.04833104</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
         <v>1199669400000</v>
       </c>
-      <c r="DA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="inlineStr">
         <is>
           <t>0.023 - 0.024</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE2" t="n">
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
         <v>0.009000001000000001</v>
       </c>
-      <c r="DF2" t="n">
+      <c r="DW2" t="n">
         <v>0.6</v>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>0.015 - 0.03</t>
         </is>
       </c>
-      <c r="DH2" t="n">
+      <c r="DY2" t="n">
         <v>-0.005999999</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DZ2" t="n">
         <v>-0.19999997</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="EA2" t="n">
         <v>50</v>
       </c>
-      <c r="DK2" t="n">
+      <c r="EB2" t="n">
         <v>1743168290</v>
       </c>
-      <c r="DL2" t="n">
+      <c r="EC2" t="n">
         <v>1743168290</v>
       </c>
-      <c r="DM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="DP2" t="n">
+      <c r="ED2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
         <v>-0.1</v>
       </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>8.499995e-05</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.0035542524</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.048305016</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1763522342</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>finmb_62168284</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>SFCE</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>Shunfeng International Clean Energy Limited</t>
-        </is>
+      <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.00015999936</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.006711382</v>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
